--- a/main/java/hospitaldatabase/dischargedpatient.xlsx
+++ b/main/java/hospitaldatabase/dischargedpatient.xlsx
@@ -53,7 +53,7 @@
     <t>Male</t>
   </si>
   <si>
-    <t>julies</t>
+    <t>johnson</t>
   </si>
   <si>
     <t>typhoid</t>
